--- a/data/trans_orig/IP18A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18A02-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33947</t>
+          <t>34248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>49939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>59738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80863</t>
+          <t>82440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104353</t>
+          <t>104587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51202</t>
+          <t>51775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>67466</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48862</t>
+          <t>47943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65056</t>
+          <t>65348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>104808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128532</t>
+          <t>126955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51908</t>
+          <t>51829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72989</t>
+          <t>71879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39231</t>
+          <t>38053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58019</t>
+          <t>58471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95886</t>
+          <t>94407</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125730</t>
+          <t>124714</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158597</t>
+          <t>159707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179678</t>
+          <t>179757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175383</t>
+          <t>174931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194171</t>
+          <t>195349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>339259</t>
+          <t>340275</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369103</t>
+          <t>370582</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>27513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27098</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44707</t>
+          <t>45363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79391</t>
+          <t>78517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91648</t>
+          <t>91767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92847</t>
+          <t>92768</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104805</t>
+          <t>104837</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176994</t>
+          <t>176338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194603</t>
+          <t>194179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17237</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135626</t>
+          <t>135946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148082</t>
+          <t>148090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150023</t>
+          <t>150237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160264</t>
+          <t>160232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289543</t>
+          <t>290133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305967</t>
+          <t>305768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123195</t>
+          <t>123311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157361</t>
+          <t>156291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111383</t>
+          <t>110984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143189</t>
+          <t>143305</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>241130</t>
+          <t>245853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288357</t>
+          <t>292357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>440657</t>
+          <t>441727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474823</t>
+          <t>474707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>480825</t>
+          <t>480709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>512631</t>
+          <t>513030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>933675</t>
+          <t>929675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>980902</t>
+          <t>976179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47901</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67260</t>
+          <t>66673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44634</t>
+          <t>45014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64085</t>
+          <t>63742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96580</t>
+          <t>97278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124144</t>
+          <t>126028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73609</t>
+          <t>74196</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92968</t>
+          <t>93161</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78363</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97814</t>
+          <t>97434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159172</t>
+          <t>157288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186736</t>
+          <t>186038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>36751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57340</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36602</t>
+          <t>37679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58084</t>
+          <t>57544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78447</t>
+          <t>77912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107657</t>
+          <t>105474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162465</t>
+          <t>164163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181884</t>
+          <t>183054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196655</t>
+          <t>197195</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>218137</t>
+          <t>217060</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366887</t>
+          <t>369070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>396097</t>
+          <t>396632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14601</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>28344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>30656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121384</t>
+          <t>121870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135613</t>
+          <t>135631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123365</t>
+          <t>123717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136894</t>
+          <t>137165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250077</t>
+          <t>250490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269651</t>
+          <t>269232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22633</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40553</t>
+          <t>41044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129537</t>
+          <t>130045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142405</t>
+          <t>141985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140684</t>
+          <t>140366</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153416</t>
+          <t>153155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274571</t>
+          <t>274080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>291751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>121942</t>
+          <t>122091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157901</t>
+          <t>157209</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>116359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151303</t>
+          <t>152330</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251680</t>
+          <t>250288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301133</t>
+          <t>300829</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505156</t>
+          <t>505848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>541115</t>
+          <t>540966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>558512</t>
+          <t>557485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>593874</t>
+          <t>593456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1071739</t>
+          <t>1072043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1121192</t>
+          <t>1122584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48194</t>
+          <t>48014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65492</t>
+          <t>65515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42374</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59574</t>
+          <t>59876</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96010</t>
+          <t>95647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120159</t>
+          <t>120886</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61986</t>
+          <t>61963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79284</t>
+          <t>79464</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58244</t>
+          <t>57942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75444</t>
+          <t>74740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125138</t>
+          <t>124411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149287</t>
+          <t>149650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41714</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59033</t>
+          <t>58404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68396</t>
+          <t>68521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95057</t>
+          <t>95132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151427</t>
+          <t>149678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168315</t>
+          <t>167609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177215</t>
+          <t>177844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>197464</t>
+          <t>197692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334331</t>
+          <t>334256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>360992</t>
+          <t>360867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30669</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51210</t>
+          <t>49162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138023</t>
+          <t>138612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152826</t>
+          <t>152927</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145570</t>
+          <t>145934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158088</t>
+          <t>158104</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>286403</t>
+          <t>288451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306944</t>
+          <t>307221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>33262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136049</t>
+          <t>136773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145967</t>
+          <t>146379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125644</t>
+          <t>124722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137544</t>
+          <t>137770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264984</t>
+          <t>265628</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281660</t>
+          <t>281733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106202</t>
+          <t>106331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137208</t>
+          <t>139069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115814</t>
+          <t>113675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147761</t>
+          <t>147131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229916</t>
+          <t>231019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277317</t>
+          <t>277629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504061</t>
+          <t>502200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>535067</t>
+          <t>534938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522158</t>
+          <t>522788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>554105</t>
+          <t>556244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033871</t>
+          <t>1033559</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1081272</t>
+          <t>1080169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23753</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,76%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20386</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24861</t>
+          <t>24206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31602</t>
+          <t>31224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47562</t>
+          <t>47878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56844</t>
+          <t>56795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30355</t>
+          <t>29968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27594</t>
+          <t>27652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35022</t>
+          <t>34771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54265</t>
+          <t>54017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64016</t>
+          <t>64172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8408</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28998</t>
+          <t>28719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38901</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47317</t>
+          <t>48455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59644</t>
+          <t>60040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>32847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54582</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74015</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86784</t>
+          <t>86709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98227</t>
+          <t>98745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113645</t>
+          <t>113120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177324</t>
+          <t>177360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196505</t>
+          <t>197811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18A02-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2007 (tasa de respuesta: 99,78%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51158</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42118</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>59494</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>42218</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34248</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49939</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>34944</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>50307</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51158</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>42333</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59738</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,51%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82440</t>
+          <t>82192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104587</t>
+          <t>105680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56523</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48187</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65563</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59496</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51775</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67466</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51407</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66770</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>58,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56523</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47943</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65348</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>52,49%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104808</t>
+          <t>103715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126955</t>
+          <t>127203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,75%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48134</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39275</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>58307</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>61567</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>51829</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>71879</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>72854</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>26,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>48134</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>38053</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>58471</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,62%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94407</t>
+          <t>95340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124714</t>
+          <t>124659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>185268</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>175095</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>194127</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>170019</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>159707</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>179757</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>158732</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>179436</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>73,41%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,62%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>185268</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>174931</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>195349</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>79,38%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340275</t>
+          <t>340330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>370582</t>
+          <t>369649</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15932</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10475</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22030</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>19981</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14263</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27513</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27088</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15932</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10834</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22903</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27522</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45363</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99739</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>93641</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>105196</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>86049</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78517</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>91767</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>78942</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>91928</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>81,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99739</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>92768</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104837</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,23%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176338</t>
+          <t>176855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194179</t>
+          <t>194127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>106030</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>106030</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>106030</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11342</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7358</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17544</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15873</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10597</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22741</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10246</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22504</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11342</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7028</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17023</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20179</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>36339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>155918</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149716</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>159902</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>142814</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>135946</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>148090</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>136183</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>148441</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>155918</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>150237</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>160232</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,22%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290133</t>
+          <t>289608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305768</t>
+          <t>305535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>126565</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>109774</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>143230</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>139640</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>123311</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>156291</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>122547</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>156306</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>23,35%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>126565</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>110984</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>143305</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245853</t>
+          <t>243041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292357</t>
+          <t>288656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>497449</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>480784</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>514240</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>79,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,05%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>680</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>458378</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>441727</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>474707</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>441712</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>475471</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>76,65%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>79,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>497449</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>480709</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>513030</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>79,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>929675</t>
+          <t>933376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>976179</t>
+          <t>978991</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,11%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2012 (tasa de respuesta: 98,2%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2012 (tasa de respuesta: 98,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53982</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44908</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>63893</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>57256</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47708</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>66673</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>48183</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>66988</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>40,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>53982</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>45014</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>63742</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97278</t>
+          <t>97346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126028</t>
+          <t>124917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -2788,67 +2788,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>88466</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78555</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97540</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>68,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>83613</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74196</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>93161</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>73881</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>92686</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>59,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>52,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>88466</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>78706</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97434</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>62,1%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157288</t>
+          <t>158399</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186038</t>
+          <t>185970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>140869</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>140869</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>140869</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,67 +3018,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>46220</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36609</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>57307</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>46152</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36751</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>55642</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>37133</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>58346</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>46220</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>37679</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>57544</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77912</t>
+          <t>79397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105474</t>
+          <t>107566</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>208519</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>197432</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>218130</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>173653</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>164163</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>183054</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>161459</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>182672</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>208519</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>197195</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>217060</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>81,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369070</t>
+          <t>366978</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>396632</t>
+          <t>395147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>254739</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>254739</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>254739</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>219805</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>219805</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>219805</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>254739</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>254739</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>254739</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18673</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12247</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25870</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>20813</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14583</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28344</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14581</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>28909</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>9,71%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>18673</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12509</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25957</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30656</t>
+          <t>30933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49398</t>
+          <t>50224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131001</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>123804</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>137427</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>129401</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>121870</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>135631</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>121305</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>135633</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>80,75%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>90,29%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>131001</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>123717</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>137165</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>82,66%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>373</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250490</t>
+          <t>249664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269232</t>
+          <t>268955</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150214</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>150214</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>150214</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,67 +3704,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>15326</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10084</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22140</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>15589</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10185</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22125</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10147</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22721</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15326</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9799</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22588</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41044</t>
+          <t>40223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>147628</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140814</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>152870</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>130045</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>141985</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>129449</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>142023</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>147628</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>140366</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>153155</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274080</t>
+          <t>274901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>291751</t>
+          <t>292111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>162954</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>162954</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>162954</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>152170</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>152170</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>152170</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>162954</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>162954</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>162954</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>134200</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>118759</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>151405</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>139810</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>122091</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>157209</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>123450</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>156938</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,09%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>134200</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>116359</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>152330</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250288</t>
+          <t>249664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300829</t>
+          <t>300786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>575615</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>558410</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>591056</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>83,27%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>753</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>523247</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>505848</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>540966</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>506119</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>539607</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>78,91%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>575615</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>557485</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>593456</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>81,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1072043</t>
+          <t>1072086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1122584</t>
+          <t>1123208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>709815</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>709815</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>709815</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>663057</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>663057</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>663057</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>709815</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>709815</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>709815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2016 (tasa de respuesta: 98,26%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2016 (tasa de respuesta: 98,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51738</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43735</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61181</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,91%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>56891</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48014</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>65515</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>48277</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>65324</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>44,63%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51738</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>43078</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95647</t>
+          <t>95765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120886</t>
+          <t>121902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66080</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56637</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74083</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70587</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>61963</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79464</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>62154</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>79201</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>55,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>48,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66080</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>57942</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74740</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>56,09%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124411</t>
+          <t>123395</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149650</t>
+          <t>149532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,96%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>127478</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>127478</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>127478</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48086</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37953</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>57329</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>33044</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25532</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>43463</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>25579</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>42227</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,11%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>48086</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>38556</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>58404</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68521</t>
+          <t>69974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95132</t>
+          <t>95641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>188162</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>178919</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>198295</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>160097</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>149678</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>167609</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>150914</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>167562</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,89%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>188162</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>177844</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>197692</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>79,65%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334256</t>
+          <t>333747</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>360867</t>
+          <t>359414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236248</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236248</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236248</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193141</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193141</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193141</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>236248</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>236248</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>236248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15724</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10087</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23046</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>23316</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16571</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30886</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16813</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>31062</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15724</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10010</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22180</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>29350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49162</t>
+          <t>49397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -5421,67 +5421,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>152390</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145068</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158027</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>146182</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138612</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>152927</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>138436</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>152685</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152390</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>145934</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158104</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,65%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>288451</t>
+          <t>288216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307221</t>
+          <t>308263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168114</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168114</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168114</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>169498</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>169498</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>169498</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>168114</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>168114</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>168114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15486</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22944</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8876</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4773</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14379</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5174</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14926</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15486</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9968</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23016</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>132252</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124794</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>137602</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>142276</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>136773</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>146379</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>136226</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>145978</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,13%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>132252</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>124722</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>137770</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,52%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>265628</t>
+          <t>264815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281733</t>
+          <t>280953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>147738</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>147738</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>147738</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151152</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151152</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151152</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>147738</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>147738</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>147738</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>115286</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>148676</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>122128</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>106331</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>139069</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>104847</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>137562</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,04%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>131035</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>113675</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>147131</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231019</t>
+          <t>231902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277629</t>
+          <t>275777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>538884</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>521243</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>554633</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>519141</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>502200</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>534938</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>503707</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>536422</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>80,96%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>538884</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>522788</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>556244</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033559</t>
+          <t>1035411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1080169</t>
+          <t>1079286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>669919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>669919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>669919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>967</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>641269</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>641269</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>641269</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>669919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>669919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>669919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por control de salud periódico en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por control de salud periódico en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6536</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8990</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7575</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4865</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10627</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8816</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6362</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11246</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>57,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8720</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5668</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11430</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>53,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,78%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>65,51%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4411</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8360</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3585</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8061</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24735</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20786</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27043</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>24613</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20137</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26896</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24206</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31224</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>53291</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47878</t>
+          <t>41726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56795</t>
+          <t>49940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4727</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9509</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3558</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7845</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>14514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30836</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26054</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33753</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>27738</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23451</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29968</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34771</t>
+          <t>28208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>60037</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54017</t>
+          <t>50603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64172</t>
+          <t>60890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1584</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8854</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33768</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28159</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37586</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>20015</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15672</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22942</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>81,61%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38752</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>54861</t>
+          <t>54233</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48455</t>
+          <t>47799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60040</t>
+          <t>59520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23565</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17290</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32281</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13605</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26560</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34095</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54546</t>
+          <t>53446</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98157</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89441</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104432</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>81085</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>73754</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>86709</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>80,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>86,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>106550</t>
+          <t>76012</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98745</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113120</t>
+          <t>82207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>187635</t>
+          <t>174169</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177360</t>
+          <t>163788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197811</t>
+          <t>182968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
